--- a/output/yearly_population_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_92_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7905</v>
+        <v>4177</v>
       </c>
       <c r="C2" t="n">
-        <v>5968</v>
+        <v>11016</v>
       </c>
       <c r="D2" t="n">
-        <v>28472</v>
+        <v>36603</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4650</v>
+        <v>3250</v>
       </c>
       <c r="C3" t="n">
-        <v>3902</v>
+        <v>5765</v>
       </c>
       <c r="D3" t="n">
-        <v>17069</v>
+        <v>18033</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3447</v>
+        <v>2819</v>
       </c>
       <c r="C4" t="n">
-        <v>3363</v>
+        <v>6053</v>
       </c>
       <c r="D4" t="n">
-        <v>8285</v>
+        <v>8482</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2112</v>
+        <v>1821</v>
       </c>
       <c r="C5" t="n">
-        <v>3597</v>
+        <v>4173</v>
       </c>
       <c r="D5" t="n">
-        <v>3164</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1229</v>
+        <v>959</v>
       </c>
       <c r="C6" t="n">
-        <v>2677</v>
+        <v>2260</v>
       </c>
       <c r="D6" t="n">
-        <v>1281</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>588</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>1408</v>
+        <v>1249</v>
       </c>
       <c r="D7" t="n">
-        <v>679</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="C8" t="n">
-        <v>581</v>
+        <v>617</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -951,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11037</v>
+        <v>6196</v>
       </c>
       <c r="C2" t="n">
-        <v>8454</v>
+        <v>14725</v>
       </c>
       <c r="D2" t="n">
-        <v>31612</v>
+        <v>38353</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4953</v>
+        <v>3009</v>
       </c>
       <c r="C3" t="n">
-        <v>4270</v>
+        <v>7206</v>
       </c>
       <c r="D3" t="n">
-        <v>17472</v>
+        <v>19346</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3396</v>
+        <v>2580</v>
       </c>
       <c r="C4" t="n">
-        <v>3556</v>
+        <v>5786</v>
       </c>
       <c r="D4" t="n">
-        <v>9387</v>
+        <v>9701</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2374</v>
+        <v>1994</v>
       </c>
       <c r="C5" t="n">
-        <v>3377</v>
+        <v>4930</v>
       </c>
       <c r="D5" t="n">
-        <v>3903</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1484</v>
+        <v>1222</v>
       </c>
       <c r="C6" t="n">
-        <v>3074</v>
+        <v>3118</v>
       </c>
       <c r="D6" t="n">
-        <v>1540</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>773</v>
+        <v>595</v>
       </c>
       <c r="C7" t="n">
-        <v>1965</v>
+        <v>1692</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -1175,10 +1175,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C8" t="n">
-        <v>945</v>
+        <v>895</v>
       </c>
       <c r="D8" t="n">
         <v>460</v>
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11810</v>
+        <v>6438</v>
       </c>
       <c r="C2" t="n">
-        <v>9368</v>
+        <v>10106</v>
       </c>
       <c r="D2" t="n">
-        <v>27876</v>
+        <v>39618</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6017</v>
+        <v>3473</v>
       </c>
       <c r="C3" t="n">
-        <v>5324</v>
+        <v>9154</v>
       </c>
       <c r="D3" t="n">
-        <v>18135</v>
+        <v>20509</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3468</v>
+        <v>2359</v>
       </c>
       <c r="C4" t="n">
-        <v>3763</v>
+        <v>6237</v>
       </c>
       <c r="D4" t="n">
-        <v>10343</v>
+        <v>10887</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2474</v>
+        <v>1992</v>
       </c>
       <c r="C5" t="n">
-        <v>3351</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="n">
-        <v>4536</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1680</v>
+        <v>1397</v>
       </c>
       <c r="C6" t="n">
-        <v>3173</v>
+        <v>3807</v>
       </c>
       <c r="D6" t="n">
-        <v>1859</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>951</v>
+        <v>763</v>
       </c>
       <c r="C7" t="n">
-        <v>2401</v>
+        <v>2278</v>
       </c>
       <c r="D7" t="n">
-        <v>856</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>448</v>
+        <v>337</v>
       </c>
       <c r="C8" t="n">
-        <v>1354</v>
+        <v>1198</v>
       </c>
       <c r="D8" t="n">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>165</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1604,7 +1604,7 @@
         <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10742</v>
+        <v>5898</v>
       </c>
       <c r="C2" t="n">
-        <v>6295</v>
+        <v>6872</v>
       </c>
       <c r="D2" t="n">
-        <v>22997</v>
+        <v>32481</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6799</v>
+        <v>4229</v>
       </c>
       <c r="C3" t="n">
-        <v>7791</v>
+        <v>12515</v>
       </c>
       <c r="D3" t="n">
-        <v>19791</v>
+        <v>22245</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2285</v>
+        <v>1840</v>
       </c>
       <c r="C4" t="n">
-        <v>5348</v>
+        <v>8461</v>
       </c>
       <c r="D4" t="n">
-        <v>9942</v>
+        <v>10174</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1552</v>
+        <v>1290</v>
       </c>
       <c r="C5" t="n">
-        <v>3109</v>
+        <v>3730</v>
       </c>
       <c r="D5" t="n">
-        <v>3084</v>
+        <v>2884</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>2352</v>
+        <v>2232</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>311</v>
       </c>
       <c r="C7" t="n">
-        <v>1326</v>
+        <v>1174</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>161</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>124</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1901,7 +1901,7 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
         <v>11</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6419</v>
+        <v>3793</v>
       </c>
       <c r="C2" t="n">
-        <v>2857</v>
+        <v>4212</v>
       </c>
       <c r="D2" t="n">
-        <v>16071</v>
+        <v>24040</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7288</v>
+        <v>4265</v>
       </c>
       <c r="C3" t="n">
-        <v>6433</v>
+        <v>9106</v>
       </c>
       <c r="D3" t="n">
-        <v>19087</v>
+        <v>22355</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3468</v>
+        <v>2400</v>
       </c>
       <c r="C4" t="n">
-        <v>6539</v>
+        <v>10396</v>
       </c>
       <c r="D4" t="n">
-        <v>11343</v>
+        <v>11914</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1739</v>
+        <v>1428</v>
       </c>
       <c r="C5" t="n">
-        <v>4139</v>
+        <v>5784</v>
       </c>
       <c r="D5" t="n">
-        <v>3905</v>
+        <v>3761</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1054</v>
+        <v>837</v>
       </c>
       <c r="C6" t="n">
-        <v>2763</v>
+        <v>2863</v>
       </c>
       <c r="D6" t="n">
-        <v>1068</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>389</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>1710</v>
+        <v>1567</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>811</v>
+        <v>784</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
         <v>96</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5865</v>
+        <v>3526</v>
       </c>
       <c r="C2" t="n">
-        <v>8259</v>
+        <v>5678</v>
       </c>
       <c r="D2" t="n">
-        <v>20789</v>
+        <v>18708</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5860</v>
+        <v>3418</v>
       </c>
       <c r="C3" t="n">
-        <v>4175</v>
+        <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>17339</v>
+        <v>21081</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4380</v>
+        <v>2737</v>
       </c>
       <c r="C4" t="n">
-        <v>6350</v>
+        <v>9548</v>
       </c>
       <c r="D4" t="n">
-        <v>12336</v>
+        <v>13255</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2194</v>
+        <v>1641</v>
       </c>
       <c r="C5" t="n">
-        <v>5204</v>
+        <v>7888</v>
       </c>
       <c r="D5" t="n">
-        <v>5000</v>
+        <v>4898</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1247</v>
+        <v>1000</v>
       </c>
       <c r="C6" t="n">
-        <v>3396</v>
+        <v>4125</v>
       </c>
       <c r="D6" t="n">
-        <v>1489</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>572</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>2190</v>
+        <v>2140</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201</v>
+        <v>151</v>
       </c>
       <c r="C8" t="n">
-        <v>1188</v>
+        <v>1105</v>
       </c>
       <c r="D8" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3475</v>
+        <v>2103</v>
       </c>
       <c r="C2" t="n">
-        <v>3780</v>
+        <v>2670</v>
       </c>
       <c r="D2" t="n">
-        <v>14345</v>
+        <v>13059</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5651</v>
+        <v>3351</v>
       </c>
       <c r="C3" t="n">
-        <v>5446</v>
+        <v>5731</v>
       </c>
       <c r="D3" t="n">
-        <v>17309</v>
+        <v>20361</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4865</v>
+        <v>3013</v>
       </c>
       <c r="C4" t="n">
-        <v>6096</v>
+        <v>9119</v>
       </c>
       <c r="D4" t="n">
-        <v>13033</v>
+        <v>14211</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2275</v>
+        <v>1730</v>
       </c>
       <c r="C5" t="n">
-        <v>6181</v>
+        <v>9452</v>
       </c>
       <c r="D5" t="n">
-        <v>5434</v>
+        <v>5186</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1047</v>
+        <v>813</v>
       </c>
       <c r="C6" t="n">
-        <v>4209</v>
+        <v>4870</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2272</v>
+        <v>2152</v>
       </c>
       <c r="D7" t="n">
-        <v>606</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>884</v>
+        <v>846</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
         <v>288</v>
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>2897</v>
       </c>
       <c r="C2" t="n">
-        <v>6017</v>
+        <v>3200</v>
       </c>
       <c r="D2" t="n">
-        <v>15525</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4056</v>
+        <v>2414</v>
       </c>
       <c r="C3" t="n">
-        <v>4156</v>
+        <v>3852</v>
       </c>
       <c r="D3" t="n">
-        <v>15742</v>
+        <v>18195</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4537</v>
+        <v>2782</v>
       </c>
       <c r="C4" t="n">
-        <v>5657</v>
+        <v>7423</v>
       </c>
       <c r="D4" t="n">
-        <v>13334</v>
+        <v>14723</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2963</v>
+        <v>2001</v>
       </c>
       <c r="C5" t="n">
-        <v>6072</v>
+        <v>9199</v>
       </c>
       <c r="D5" t="n">
-        <v>6436</v>
+        <v>6327</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1369</v>
+        <v>1051</v>
       </c>
       <c r="C6" t="n">
-        <v>5103</v>
+        <v>6765</v>
       </c>
       <c r="D6" t="n">
-        <v>2011</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>3071</v>
+        <v>3258</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1417</v>
+        <v>1323</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3103,7 +3103,7 @@
         <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3428</v>
+        <v>1957</v>
       </c>
       <c r="C2" t="n">
-        <v>3555</v>
+        <v>2672</v>
       </c>
       <c r="D2" t="n">
-        <v>11087</v>
+        <v>10381</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3734</v>
+        <v>2250</v>
       </c>
       <c r="C3" t="n">
-        <v>4488</v>
+        <v>3308</v>
       </c>
       <c r="D3" t="n">
-        <v>14859</v>
+        <v>16722</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4047</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>5028</v>
+        <v>6005</v>
       </c>
       <c r="D4" t="n">
-        <v>13380</v>
+        <v>14850</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3243</v>
+        <v>2148</v>
       </c>
       <c r="C5" t="n">
-        <v>6023</v>
+        <v>8730</v>
       </c>
       <c r="D5" t="n">
-        <v>7158</v>
+        <v>7082</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1661</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="n">
-        <v>5624</v>
+        <v>7776</v>
       </c>
       <c r="D6" t="n">
-        <v>2408</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>3798</v>
+        <v>4305</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1835</v>
+        <v>1745</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>572</v>
+        <v>522</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>3742</v>
       </c>
       <c r="C2" t="n">
-        <v>8524</v>
+        <v>7459</v>
       </c>
       <c r="D2" t="n">
-        <v>14285</v>
+        <v>22708</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3046</v>
+        <v>1809</v>
       </c>
       <c r="C3" t="n">
-        <v>3677</v>
+        <v>2750</v>
       </c>
       <c r="D3" t="n">
-        <v>13455</v>
+        <v>14890</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3452</v>
+        <v>2078</v>
       </c>
       <c r="C4" t="n">
-        <v>4690</v>
+        <v>4766</v>
       </c>
       <c r="D4" t="n">
-        <v>13186</v>
+        <v>14668</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3209</v>
+        <v>2082</v>
       </c>
       <c r="C5" t="n">
-        <v>5486</v>
+        <v>7475</v>
       </c>
       <c r="D5" t="n">
-        <v>7707</v>
+        <v>7910</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2048</v>
+        <v>1405</v>
       </c>
       <c r="C6" t="n">
-        <v>5732</v>
+        <v>8069</v>
       </c>
       <c r="D6" t="n">
-        <v>3015</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>704</v>
+        <v>498</v>
       </c>
       <c r="C7" t="n">
-        <v>4494</v>
+        <v>5561</v>
       </c>
       <c r="D7" t="n">
-        <v>1000</v>
+        <v>935</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>2564</v>
+        <v>2622</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>998</v>
+        <v>922</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7795</v>
+        <v>4682</v>
       </c>
       <c r="C2" t="n">
-        <v>2807</v>
+        <v>5010</v>
       </c>
       <c r="D2" t="n">
-        <v>13969</v>
+        <v>10339</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3890</v>
+        <v>2704</v>
       </c>
       <c r="C2" t="n">
-        <v>4773</v>
+        <v>4296</v>
       </c>
       <c r="D2" t="n">
-        <v>10513</v>
+        <v>16895</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4210</v>
+        <v>2513</v>
       </c>
       <c r="C3" t="n">
-        <v>5152</v>
+        <v>4046</v>
       </c>
       <c r="D3" t="n">
-        <v>14717</v>
+        <v>16551</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4699</v>
+        <v>2982</v>
       </c>
       <c r="C4" t="n">
-        <v>6558</v>
+        <v>7207</v>
       </c>
       <c r="D4" t="n">
-        <v>13548</v>
+        <v>14993</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2010</v>
+        <v>1336</v>
       </c>
       <c r="C5" t="n">
-        <v>8071</v>
+        <v>11213</v>
       </c>
       <c r="D5" t="n">
-        <v>7100</v>
+        <v>7087</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>650</v>
+        <v>460</v>
       </c>
       <c r="C6" t="n">
-        <v>5583</v>
+        <v>6952</v>
       </c>
       <c r="D6" t="n">
-        <v>2329</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>2512</v>
+        <v>2569</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>903</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7566</v>
+        <v>6009</v>
       </c>
       <c r="C2" t="n">
-        <v>5644</v>
+        <v>2694</v>
       </c>
       <c r="D2" t="n">
-        <v>22782</v>
+        <v>14963</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3310</v>
+        <v>1990</v>
       </c>
       <c r="C3" t="n">
-        <v>1414</v>
+        <v>2525</v>
       </c>
       <c r="D3" t="n">
-        <v>2986</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5810</v>
+        <v>4391</v>
       </c>
       <c r="C2" t="n">
-        <v>5052</v>
+        <v>4721</v>
       </c>
       <c r="D2" t="n">
-        <v>27034</v>
+        <v>16799</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4468</v>
+        <v>3282</v>
       </c>
       <c r="C3" t="n">
-        <v>3283</v>
+        <v>2257</v>
       </c>
       <c r="D3" t="n">
-        <v>6091</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1472</v>
+        <v>898</v>
       </c>
       <c r="C4" t="n">
-        <v>874</v>
+        <v>1546</v>
       </c>
       <c r="D4" t="n">
-        <v>1783</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5641</v>
+        <v>4823</v>
       </c>
       <c r="C2" t="n">
-        <v>8561</v>
+        <v>6054</v>
       </c>
       <c r="D2" t="n">
-        <v>24162</v>
+        <v>25218</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4218</v>
+        <v>3154</v>
       </c>
       <c r="C3" t="n">
-        <v>3676</v>
+        <v>3116</v>
       </c>
       <c r="D3" t="n">
-        <v>9003</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529</v>
+        <v>1795</v>
       </c>
       <c r="C4" t="n">
-        <v>2220</v>
+        <v>1901</v>
       </c>
       <c r="D4" t="n">
-        <v>2555</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>651</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>572</v>
+        <v>953</v>
       </c>
       <c r="D5" t="n">
-        <v>1256</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6574</v>
+        <v>5841</v>
       </c>
       <c r="C2" t="n">
-        <v>6168</v>
+        <v>5686</v>
       </c>
       <c r="D2" t="n">
-        <v>19200</v>
+        <v>40475</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4025</v>
+        <v>3237</v>
       </c>
       <c r="C3" t="n">
-        <v>5388</v>
+        <v>4046</v>
       </c>
       <c r="D3" t="n">
-        <v>10673</v>
+        <v>8499</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2874</v>
+        <v>2088</v>
       </c>
       <c r="C4" t="n">
-        <v>2956</v>
+        <v>2526</v>
       </c>
       <c r="D4" t="n">
-        <v>3653</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1306</v>
+        <v>925</v>
       </c>
       <c r="C5" t="n">
-        <v>1408</v>
+        <v>1424</v>
       </c>
       <c r="D5" t="n">
-        <v>1430</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>343</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
-        <v>435</v>
+        <v>636</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>945</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7548</v>
+        <v>6851</v>
       </c>
       <c r="C2" t="n">
-        <v>4552</v>
+        <v>11205</v>
       </c>
       <c r="D2" t="n">
-        <v>35271</v>
+        <v>35620</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>3289</v>
       </c>
       <c r="C3" t="n">
-        <v>4740</v>
+        <v>4011</v>
       </c>
       <c r="D3" t="n">
-        <v>10554</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2128</v>
+        <v>1663</v>
       </c>
       <c r="C4" t="n">
-        <v>3497</v>
+        <v>2771</v>
       </c>
       <c r="D4" t="n">
-        <v>4177</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1090</v>
+        <v>784</v>
       </c>
       <c r="C5" t="n">
-        <v>1629</v>
+        <v>1457</v>
       </c>
       <c r="D5" t="n">
-        <v>1453</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>393</v>
+        <v>279</v>
       </c>
       <c r="C6" t="n">
-        <v>620</v>
+        <v>702</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>765</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7469</v>
+        <v>5148</v>
       </c>
       <c r="C2" t="n">
-        <v>2940</v>
+        <v>8599</v>
       </c>
       <c r="D2" t="n">
-        <v>31052</v>
+        <v>35568</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4731</v>
+        <v>4248</v>
       </c>
       <c r="C3" t="n">
-        <v>4014</v>
+        <v>7123</v>
       </c>
       <c r="D3" t="n">
-        <v>14211</v>
+        <v>15256</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2614</v>
+        <v>2193</v>
       </c>
       <c r="C4" t="n">
-        <v>4142</v>
+        <v>3475</v>
       </c>
       <c r="D4" t="n">
-        <v>5295</v>
+        <v>4965</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1428</v>
+        <v>1098</v>
       </c>
       <c r="C5" t="n">
-        <v>2706</v>
+        <v>2208</v>
       </c>
       <c r="D5" t="n">
-        <v>1957</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>692</v>
+        <v>493</v>
       </c>
       <c r="C6" t="n">
-        <v>1193</v>
+        <v>1121</v>
       </c>
       <c r="D6" t="n">
-        <v>896</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>226</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>461</v>
+        <v>539</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
         <v>175</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6408</v>
+        <v>3996</v>
       </c>
       <c r="C2" t="n">
-        <v>5957</v>
+        <v>6366</v>
       </c>
       <c r="D2" t="n">
-        <v>31049</v>
+        <v>29590</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4983</v>
+        <v>3868</v>
       </c>
       <c r="C3" t="n">
-        <v>2967</v>
+        <v>6862</v>
       </c>
       <c r="D3" t="n">
-        <v>15882</v>
+        <v>17407</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3133</v>
+        <v>2781</v>
       </c>
       <c r="C4" t="n">
-        <v>3983</v>
+        <v>5503</v>
       </c>
       <c r="D4" t="n">
-        <v>6845</v>
+        <v>6742</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1781</v>
+        <v>1434</v>
       </c>
       <c r="C5" t="n">
-        <v>3409</v>
+        <v>2867</v>
       </c>
       <c r="D5" t="n">
-        <v>2487</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>958</v>
+        <v>727</v>
       </c>
       <c r="C6" t="n">
-        <v>1992</v>
+        <v>1692</v>
       </c>
       <c r="D6" t="n">
-        <v>1076</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>406</v>
+        <v>292</v>
       </c>
       <c r="C7" t="n">
-        <v>848</v>
+        <v>841</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_92_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4177</v>
+        <v>7011</v>
       </c>
       <c r="C2" t="n">
-        <v>11016</v>
+        <v>4377</v>
       </c>
       <c r="D2" t="n">
-        <v>36603</v>
+        <v>32101</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3250</v>
+        <v>4465</v>
       </c>
       <c r="C3" t="n">
-        <v>5765</v>
+        <v>4132</v>
       </c>
       <c r="D3" t="n">
-        <v>18033</v>
+        <v>15128</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2819</v>
+        <v>3238</v>
       </c>
       <c r="C4" t="n">
-        <v>6053</v>
+        <v>3928</v>
       </c>
       <c r="D4" t="n">
-        <v>8482</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1821</v>
+        <v>2059</v>
       </c>
       <c r="C5" t="n">
-        <v>4173</v>
+        <v>3364</v>
       </c>
       <c r="D5" t="n">
-        <v>2907</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>959</v>
+        <v>1228</v>
       </c>
       <c r="C6" t="n">
-        <v>2260</v>
+        <v>2809</v>
       </c>
       <c r="D6" t="n">
-        <v>1174</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>618</v>
       </c>
       <c r="C7" t="n">
-        <v>1249</v>
+        <v>1526</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>166</v>
+        <v>229</v>
       </c>
       <c r="C8" t="n">
-        <v>617</v>
+        <v>648</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>246</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6196</v>
+        <v>8973</v>
       </c>
       <c r="C2" t="n">
-        <v>14725</v>
+        <v>5285</v>
       </c>
       <c r="D2" t="n">
-        <v>38353</v>
+        <v>27606</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3009</v>
+        <v>4580</v>
       </c>
       <c r="C3" t="n">
-        <v>7206</v>
+        <v>3729</v>
       </c>
       <c r="D3" t="n">
-        <v>19346</v>
+        <v>16419</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2580</v>
+        <v>3263</v>
       </c>
       <c r="C4" t="n">
-        <v>5786</v>
+        <v>3908</v>
       </c>
       <c r="D4" t="n">
-        <v>9701</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1994</v>
+        <v>2272</v>
       </c>
       <c r="C5" t="n">
-        <v>4930</v>
+        <v>3564</v>
       </c>
       <c r="D5" t="n">
-        <v>3728</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>1453</v>
       </c>
       <c r="C6" t="n">
-        <v>3118</v>
+        <v>3009</v>
       </c>
       <c r="D6" t="n">
-        <v>1412</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>595</v>
+        <v>802</v>
       </c>
       <c r="C7" t="n">
-        <v>1692</v>
+        <v>2116</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>249</v>
+        <v>346</v>
       </c>
       <c r="C8" t="n">
-        <v>895</v>
+        <v>1034</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6438</v>
+        <v>9839</v>
       </c>
       <c r="C2" t="n">
-        <v>10106</v>
+        <v>7338</v>
       </c>
       <c r="D2" t="n">
-        <v>39618</v>
+        <v>27523</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3473</v>
+        <v>5179</v>
       </c>
       <c r="C3" t="n">
-        <v>9154</v>
+        <v>3884</v>
       </c>
       <c r="D3" t="n">
-        <v>20509</v>
+        <v>16773</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2359</v>
+        <v>3245</v>
       </c>
       <c r="C4" t="n">
-        <v>6237</v>
+        <v>3708</v>
       </c>
       <c r="D4" t="n">
-        <v>10887</v>
+        <v>8885</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1992</v>
+        <v>2379</v>
       </c>
       <c r="C5" t="n">
-        <v>5197</v>
+        <v>3641</v>
       </c>
       <c r="D5" t="n">
-        <v>4438</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1397</v>
+        <v>1649</v>
       </c>
       <c r="C6" t="n">
-        <v>3807</v>
+        <v>3186</v>
       </c>
       <c r="D6" t="n">
-        <v>1726</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>763</v>
+        <v>958</v>
       </c>
       <c r="C7" t="n">
-        <v>2278</v>
+        <v>2491</v>
       </c>
       <c r="D7" t="n">
-        <v>810</v>
+        <v>792</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>337</v>
+        <v>466</v>
       </c>
       <c r="C8" t="n">
-        <v>1198</v>
+        <v>1458</v>
       </c>
       <c r="D8" t="n">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="C9" t="n">
-        <v>610</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
         <v>11</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5898</v>
+        <v>8943</v>
       </c>
       <c r="C2" t="n">
-        <v>6872</v>
+        <v>4872</v>
       </c>
       <c r="D2" t="n">
-        <v>32481</v>
+        <v>22442</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4229</v>
+        <v>6118</v>
       </c>
       <c r="C3" t="n">
-        <v>12515</v>
+        <v>6186</v>
       </c>
       <c r="D3" t="n">
-        <v>22245</v>
+        <v>18322</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1840</v>
+        <v>2198</v>
       </c>
       <c r="C4" t="n">
-        <v>8461</v>
+        <v>5595</v>
       </c>
       <c r="D4" t="n">
-        <v>10174</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1290</v>
+        <v>1523</v>
       </c>
       <c r="C5" t="n">
-        <v>3730</v>
+        <v>3122</v>
       </c>
       <c r="D5" t="n">
-        <v>2884</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>885</v>
       </c>
       <c r="C6" t="n">
-        <v>2232</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>311</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>1174</v>
+        <v>1428</v>
       </c>
       <c r="D7" t="n">
-        <v>482</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>597</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3793</v>
+        <v>5390</v>
       </c>
       <c r="C2" t="n">
-        <v>4212</v>
+        <v>2508</v>
       </c>
       <c r="D2" t="n">
-        <v>24040</v>
+        <v>17002</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4265</v>
+        <v>6340</v>
       </c>
       <c r="C3" t="n">
-        <v>9106</v>
+        <v>5035</v>
       </c>
       <c r="D3" t="n">
-        <v>22355</v>
+        <v>18006</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>3262</v>
       </c>
       <c r="C4" t="n">
-        <v>10396</v>
+        <v>5977</v>
       </c>
       <c r="D4" t="n">
-        <v>11914</v>
+        <v>9905</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1428</v>
+        <v>1683</v>
       </c>
       <c r="C5" t="n">
-        <v>5784</v>
+        <v>4251</v>
       </c>
       <c r="D5" t="n">
-        <v>3761</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>837</v>
+        <v>1068</v>
       </c>
       <c r="C6" t="n">
-        <v>2863</v>
+        <v>2807</v>
       </c>
       <c r="D6" t="n">
-        <v>1007</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>1567</v>
+        <v>1841</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>784</v>
+        <v>882</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
         <v>259</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,10 +2167,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3526</v>
+        <v>5712</v>
       </c>
       <c r="C2" t="n">
-        <v>5678</v>
+        <v>6619</v>
       </c>
       <c r="D2" t="n">
-        <v>18708</v>
+        <v>15881</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3418</v>
+        <v>4976</v>
       </c>
       <c r="C3" t="n">
-        <v>6035</v>
+        <v>3355</v>
       </c>
       <c r="D3" t="n">
-        <v>21081</v>
+        <v>16622</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2737</v>
+        <v>3990</v>
       </c>
       <c r="C4" t="n">
-        <v>9548</v>
+        <v>5373</v>
       </c>
       <c r="D4" t="n">
-        <v>13255</v>
+        <v>11003</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1641</v>
+        <v>2091</v>
       </c>
       <c r="C5" t="n">
-        <v>7888</v>
+        <v>5048</v>
       </c>
       <c r="D5" t="n">
-        <v>4898</v>
+        <v>4280</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1000</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="n">
-        <v>4125</v>
+        <v>3444</v>
       </c>
       <c r="D6" t="n">
-        <v>1390</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>600</v>
       </c>
       <c r="C7" t="n">
-        <v>2140</v>
+        <v>2293</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C8" t="n">
-        <v>1105</v>
+        <v>1294</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>576</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2103</v>
+        <v>3342</v>
       </c>
       <c r="C2" t="n">
-        <v>2670</v>
+        <v>3001</v>
       </c>
       <c r="D2" t="n">
-        <v>13059</v>
+        <v>11005</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3351</v>
+        <v>5020</v>
       </c>
       <c r="C3" t="n">
-        <v>5731</v>
+        <v>4391</v>
       </c>
       <c r="D3" t="n">
-        <v>20361</v>
+        <v>16140</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3013</v>
+        <v>4383</v>
       </c>
       <c r="C4" t="n">
-        <v>9119</v>
+        <v>5079</v>
       </c>
       <c r="D4" t="n">
-        <v>14211</v>
+        <v>11736</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1730</v>
+        <v>2196</v>
       </c>
       <c r="C5" t="n">
-        <v>9452</v>
+        <v>5797</v>
       </c>
       <c r="D5" t="n">
-        <v>5186</v>
+        <v>4659</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>1075</v>
       </c>
       <c r="C6" t="n">
-        <v>4870</v>
+        <v>4335</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="C7" t="n">
-        <v>2152</v>
+        <v>2422</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>846</v>
+        <v>982</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2897</v>
+        <v>4410</v>
       </c>
       <c r="C2" t="n">
-        <v>3200</v>
+        <v>7217</v>
       </c>
       <c r="D2" t="n">
-        <v>12721</v>
+        <v>10942</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2414</v>
+        <v>3673</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>3313</v>
       </c>
       <c r="D3" t="n">
-        <v>18195</v>
+        <v>14445</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>4068</v>
       </c>
       <c r="C4" t="n">
-        <v>7423</v>
+        <v>4636</v>
       </c>
       <c r="D4" t="n">
-        <v>14723</v>
+        <v>12097</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2001</v>
+        <v>2778</v>
       </c>
       <c r="C5" t="n">
-        <v>9199</v>
+        <v>5394</v>
       </c>
       <c r="D5" t="n">
-        <v>6327</v>
+        <v>5604</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1051</v>
+        <v>1374</v>
       </c>
       <c r="C6" t="n">
-        <v>6765</v>
+        <v>4981</v>
       </c>
       <c r="D6" t="n">
-        <v>1853</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>3258</v>
+        <v>3274</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>1323</v>
+        <v>1551</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>457</v>
+        <v>524</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1957</v>
+        <v>3408</v>
       </c>
       <c r="C2" t="n">
-        <v>2672</v>
+        <v>4652</v>
       </c>
       <c r="D2" t="n">
-        <v>10381</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2250</v>
+        <v>3433</v>
       </c>
       <c r="C3" t="n">
-        <v>3308</v>
+        <v>4462</v>
       </c>
       <c r="D3" t="n">
-        <v>16722</v>
+        <v>13326</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>3635</v>
       </c>
       <c r="C4" t="n">
-        <v>6005</v>
+        <v>4101</v>
       </c>
       <c r="D4" t="n">
-        <v>14850</v>
+        <v>12160</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2148</v>
+        <v>3013</v>
       </c>
       <c r="C5" t="n">
-        <v>8730</v>
+        <v>5197</v>
       </c>
       <c r="D5" t="n">
-        <v>7082</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1217</v>
+        <v>1652</v>
       </c>
       <c r="C6" t="n">
-        <v>7776</v>
+        <v>5324</v>
       </c>
       <c r="D6" t="n">
-        <v>2271</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>4305</v>
+        <v>3948</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>1745</v>
+        <v>2006</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>522</v>
+        <v>647</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3742</v>
+        <v>5572</v>
       </c>
       <c r="C2" t="n">
-        <v>7459</v>
+        <v>7026</v>
       </c>
       <c r="D2" t="n">
-        <v>22708</v>
+        <v>8868</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1809</v>
+        <v>2876</v>
       </c>
       <c r="C3" t="n">
-        <v>2750</v>
+        <v>4019</v>
       </c>
       <c r="D3" t="n">
-        <v>14890</v>
+        <v>11849</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2078</v>
+        <v>3093</v>
       </c>
       <c r="C4" t="n">
-        <v>4766</v>
+        <v>4178</v>
       </c>
       <c r="D4" t="n">
-        <v>14668</v>
+        <v>11969</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2082</v>
+        <v>2980</v>
       </c>
       <c r="C5" t="n">
-        <v>7475</v>
+        <v>4615</v>
       </c>
       <c r="D5" t="n">
-        <v>7910</v>
+        <v>6898</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1405</v>
+        <v>1987</v>
       </c>
       <c r="C6" t="n">
-        <v>8069</v>
+        <v>5275</v>
       </c>
       <c r="D6" t="n">
-        <v>2842</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>498</v>
+        <v>737</v>
       </c>
       <c r="C7" t="n">
-        <v>5561</v>
+        <v>4485</v>
       </c>
       <c r="D7" t="n">
-        <v>935</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>2622</v>
+        <v>2748</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>922</v>
+        <v>1119</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4682</v>
+        <v>8248</v>
       </c>
       <c r="C2" t="n">
-        <v>5010</v>
+        <v>3960</v>
       </c>
       <c r="D2" t="n">
-        <v>10339</v>
+        <v>6139</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2704</v>
+        <v>3901</v>
       </c>
       <c r="C2" t="n">
-        <v>4296</v>
+        <v>3879</v>
       </c>
       <c r="D2" t="n">
-        <v>16895</v>
+        <v>6526</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2513</v>
+        <v>3952</v>
       </c>
       <c r="C3" t="n">
-        <v>4046</v>
+        <v>5099</v>
       </c>
       <c r="D3" t="n">
-        <v>16551</v>
+        <v>12632</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2982</v>
+        <v>4328</v>
       </c>
       <c r="C4" t="n">
-        <v>7207</v>
+        <v>5841</v>
       </c>
       <c r="D4" t="n">
-        <v>14993</v>
+        <v>12390</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1336</v>
+        <v>1973</v>
       </c>
       <c r="C5" t="n">
-        <v>11213</v>
+        <v>7133</v>
       </c>
       <c r="D5" t="n">
-        <v>7087</v>
+        <v>6322</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>460</v>
+        <v>680</v>
       </c>
       <c r="C6" t="n">
-        <v>6952</v>
+        <v>5532</v>
       </c>
       <c r="D6" t="n">
-        <v>2189</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>2569</v>
+        <v>2693</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>903</v>
+        <v>1096</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>353</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6009</v>
+        <v>7623</v>
       </c>
       <c r="C2" t="n">
-        <v>2694</v>
+        <v>4723</v>
       </c>
       <c r="D2" t="n">
-        <v>14963</v>
+        <v>17503</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1990</v>
+        <v>3502</v>
       </c>
       <c r="C3" t="n">
-        <v>2525</v>
+        <v>2027</v>
       </c>
       <c r="D3" t="n">
-        <v>2376</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4391</v>
+        <v>5661</v>
       </c>
       <c r="C2" t="n">
-        <v>4721</v>
+        <v>6407</v>
       </c>
       <c r="D2" t="n">
-        <v>16799</v>
+        <v>14167</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3282</v>
+        <v>4572</v>
       </c>
       <c r="C3" t="n">
-        <v>2257</v>
+        <v>3063</v>
       </c>
       <c r="D3" t="n">
-        <v>4315</v>
+        <v>4207</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>898</v>
+        <v>1555</v>
       </c>
       <c r="C4" t="n">
-        <v>1546</v>
+        <v>1230</v>
       </c>
       <c r="D4" t="n">
-        <v>1660</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="5">
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
         <v>411</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4823</v>
+        <v>5872</v>
       </c>
       <c r="C2" t="n">
-        <v>6054</v>
+        <v>8914</v>
       </c>
       <c r="D2" t="n">
-        <v>25218</v>
+        <v>30063</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3154</v>
+        <v>4205</v>
       </c>
       <c r="C3" t="n">
-        <v>3116</v>
+        <v>4229</v>
       </c>
       <c r="D3" t="n">
-        <v>6001</v>
+        <v>5497</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1795</v>
+        <v>2597</v>
       </c>
       <c r="C4" t="n">
-        <v>1901</v>
+        <v>2242</v>
       </c>
       <c r="D4" t="n">
-        <v>2103</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>429</v>
+        <v>698</v>
       </c>
       <c r="C5" t="n">
-        <v>953</v>
+        <v>765</v>
       </c>
       <c r="D5" t="n">
-        <v>1240</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
         <v>303</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
         <v>462</v>
@@ -5235,7 +5235,7 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
         <v>372</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,10 +5274,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>211</v>
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5841</v>
+        <v>5682</v>
       </c>
       <c r="C2" t="n">
-        <v>5686</v>
+        <v>4919</v>
       </c>
       <c r="D2" t="n">
-        <v>40475</v>
+        <v>22150</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3237</v>
+        <v>4106</v>
       </c>
       <c r="C3" t="n">
-        <v>4046</v>
+        <v>5779</v>
       </c>
       <c r="D3" t="n">
-        <v>8499</v>
+        <v>8844</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2088</v>
+        <v>2900</v>
       </c>
       <c r="C4" t="n">
-        <v>2526</v>
+        <v>3242</v>
       </c>
       <c r="D4" t="n">
-        <v>2729</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>925</v>
+        <v>1356</v>
       </c>
       <c r="C5" t="n">
-        <v>1424</v>
+        <v>1528</v>
       </c>
       <c r="D5" t="n">
-        <v>1359</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>251</v>
+        <v>362</v>
       </c>
       <c r="C6" t="n">
-        <v>636</v>
+        <v>534</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,7 +5532,7 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
         <v>484</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
         <v>378</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6851</v>
+        <v>6940</v>
       </c>
       <c r="C2" t="n">
-        <v>11205</v>
+        <v>2949</v>
       </c>
       <c r="D2" t="n">
-        <v>35620</v>
+        <v>24915</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3289</v>
+        <v>3591</v>
       </c>
       <c r="C3" t="n">
-        <v>4011</v>
+        <v>4374</v>
       </c>
       <c r="D3" t="n">
-        <v>12003</v>
+        <v>9637</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1663</v>
+        <v>2161</v>
       </c>
       <c r="C4" t="n">
-        <v>2771</v>
+        <v>3777</v>
       </c>
       <c r="D4" t="n">
-        <v>3205</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>784</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="n">
-        <v>1457</v>
+        <v>1781</v>
       </c>
       <c r="D5" t="n">
-        <v>1271</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>279</v>
+        <v>410</v>
       </c>
       <c r="C6" t="n">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D6" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
         <v>270</v>
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5148</v>
+        <v>7105</v>
       </c>
       <c r="C2" t="n">
-        <v>8599</v>
+        <v>7197</v>
       </c>
       <c r="D2" t="n">
-        <v>35568</v>
+        <v>25806</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4248</v>
+        <v>4380</v>
       </c>
       <c r="C3" t="n">
-        <v>7123</v>
+        <v>3021</v>
       </c>
       <c r="D3" t="n">
-        <v>15256</v>
+        <v>11601</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2193</v>
+        <v>2505</v>
       </c>
       <c r="C4" t="n">
-        <v>3475</v>
+        <v>4065</v>
       </c>
       <c r="D4" t="n">
-        <v>4965</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1098</v>
+        <v>1471</v>
       </c>
       <c r="C5" t="n">
-        <v>2208</v>
+        <v>2931</v>
       </c>
       <c r="D5" t="n">
-        <v>1622</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>493</v>
+        <v>710</v>
       </c>
       <c r="C6" t="n">
-        <v>1121</v>
+        <v>1311</v>
       </c>
       <c r="D6" t="n">
-        <v>843</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C7" t="n">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
         <v>211</v>
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>175</v>
@@ -6199,7 +6199,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6227,7 +6227,7 @@
         <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3996</v>
+        <v>6251</v>
       </c>
       <c r="C2" t="n">
-        <v>6366</v>
+        <v>4863</v>
       </c>
       <c r="D2" t="n">
-        <v>29590</v>
+        <v>32829</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3868</v>
+        <v>4707</v>
       </c>
       <c r="C3" t="n">
-        <v>6862</v>
+        <v>4614</v>
       </c>
       <c r="D3" t="n">
-        <v>17407</v>
+        <v>13038</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2781</v>
+        <v>2975</v>
       </c>
       <c r="C4" t="n">
-        <v>5503</v>
+        <v>3379</v>
       </c>
       <c r="D4" t="n">
-        <v>6742</v>
+        <v>5625</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1744</v>
       </c>
       <c r="C5" t="n">
-        <v>2867</v>
+        <v>3501</v>
       </c>
       <c r="D5" t="n">
-        <v>2214</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>999</v>
       </c>
       <c r="C6" t="n">
-        <v>1692</v>
+        <v>2166</v>
       </c>
       <c r="D6" t="n">
-        <v>973</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>416</v>
       </c>
       <c r="C7" t="n">
-        <v>841</v>
+        <v>930</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C8" t="n">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>293</v>
@@ -6510,7 +6510,7 @@
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6538,7 +6538,7 @@
         <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>

--- a/output/yearly_population_iteration_92_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_92_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7011</v>
+        <v>504</v>
       </c>
       <c r="C2" t="n">
-        <v>4377</v>
+        <v>2989</v>
       </c>
       <c r="D2" t="n">
-        <v>32101</v>
+        <v>16310</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4465</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>4132</v>
+        <v>8593</v>
       </c>
       <c r="D3" t="n">
-        <v>15128</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3238</v>
+        <v>841</v>
       </c>
       <c r="C4" t="n">
-        <v>3928</v>
+        <v>10274</v>
       </c>
       <c r="D4" t="n">
-        <v>6806</v>
+        <v>5194</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2059</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>3364</v>
+        <v>4963</v>
       </c>
       <c r="D5" t="n">
-        <v>2592</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1228</v>
+        <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>2809</v>
+        <v>1679</v>
       </c>
       <c r="D6" t="n">
-        <v>1127</v>
+        <v>739</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>618</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1526</v>
+        <v>665</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>648</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8973</v>
+        <v>1318</v>
       </c>
       <c r="C2" t="n">
-        <v>5285</v>
+        <v>6194</v>
       </c>
       <c r="D2" t="n">
-        <v>27606</v>
+        <v>14989</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4580</v>
+        <v>690</v>
       </c>
       <c r="C3" t="n">
-        <v>3729</v>
+        <v>4934</v>
       </c>
       <c r="D3" t="n">
-        <v>16419</v>
+        <v>12501</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3263</v>
+        <v>824</v>
       </c>
       <c r="C4" t="n">
-        <v>3908</v>
+        <v>9140</v>
       </c>
       <c r="D4" t="n">
-        <v>7891</v>
+        <v>6409</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2272</v>
+        <v>540</v>
       </c>
       <c r="C5" t="n">
-        <v>3564</v>
+        <v>7711</v>
       </c>
       <c r="D5" t="n">
-        <v>3200</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1453</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>3009</v>
+        <v>3316</v>
       </c>
       <c r="D6" t="n">
-        <v>1325</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>802</v>
+        <v>119</v>
       </c>
       <c r="C7" t="n">
-        <v>2116</v>
+        <v>1158</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1034</v>
+        <v>494</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>445</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9839</v>
+        <v>694</v>
       </c>
       <c r="C2" t="n">
-        <v>7338</v>
+        <v>2593</v>
       </c>
       <c r="D2" t="n">
-        <v>27523</v>
+        <v>10132</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5179</v>
+        <v>834</v>
       </c>
       <c r="C3" t="n">
-        <v>3884</v>
+        <v>5222</v>
       </c>
       <c r="D3" t="n">
-        <v>16773</v>
+        <v>12479</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3245</v>
+        <v>888</v>
       </c>
       <c r="C4" t="n">
-        <v>3708</v>
+        <v>8259</v>
       </c>
       <c r="D4" t="n">
-        <v>8885</v>
+        <v>7285</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2379</v>
+        <v>544</v>
       </c>
       <c r="C5" t="n">
-        <v>3641</v>
+        <v>9045</v>
       </c>
       <c r="D5" t="n">
-        <v>3823</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1649</v>
+        <v>225</v>
       </c>
       <c r="C6" t="n">
-        <v>3186</v>
+        <v>4370</v>
       </c>
       <c r="D6" t="n">
-        <v>1564</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>958</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2491</v>
+        <v>1138</v>
       </c>
       <c r="D7" t="n">
-        <v>792</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>466</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1458</v>
+        <v>485</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>671</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8943</v>
+        <v>375</v>
       </c>
       <c r="C2" t="n">
-        <v>4872</v>
+        <v>6794</v>
       </c>
       <c r="D2" t="n">
-        <v>22442</v>
+        <v>10875</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6118</v>
+        <v>653</v>
       </c>
       <c r="C3" t="n">
-        <v>6186</v>
+        <v>3417</v>
       </c>
       <c r="D3" t="n">
-        <v>18322</v>
+        <v>11363</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2198</v>
+        <v>766</v>
       </c>
       <c r="C4" t="n">
-        <v>5595</v>
+        <v>6562</v>
       </c>
       <c r="D4" t="n">
-        <v>8491</v>
+        <v>7961</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1523</v>
+        <v>624</v>
       </c>
       <c r="C5" t="n">
-        <v>3122</v>
+        <v>8551</v>
       </c>
       <c r="D5" t="n">
-        <v>2597</v>
+        <v>3363</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>885</v>
+        <v>324</v>
       </c>
       <c r="C6" t="n">
-        <v>2441</v>
+        <v>6610</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>1428</v>
+        <v>2585</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>657</v>
+        <v>756</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5390</v>
+        <v>172</v>
       </c>
       <c r="C2" t="n">
-        <v>2508</v>
+        <v>4325</v>
       </c>
       <c r="D2" t="n">
-        <v>17002</v>
+        <v>8491</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6340</v>
+        <v>481</v>
       </c>
       <c r="C3" t="n">
-        <v>5035</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>18006</v>
+        <v>10751</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3262</v>
+        <v>671</v>
       </c>
       <c r="C4" t="n">
-        <v>5977</v>
+        <v>5165</v>
       </c>
       <c r="D4" t="n">
-        <v>9905</v>
+        <v>8285</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1683</v>
+        <v>654</v>
       </c>
       <c r="C5" t="n">
-        <v>4251</v>
+        <v>7880</v>
       </c>
       <c r="D5" t="n">
-        <v>3303</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1068</v>
+        <v>389</v>
       </c>
       <c r="C6" t="n">
-        <v>2807</v>
+        <v>7636</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1841</v>
+        <v>3905</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>1184</v>
       </c>
       <c r="D8" t="n">
-        <v>345</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>432</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5712</v>
+        <v>296</v>
       </c>
       <c r="C2" t="n">
-        <v>6619</v>
+        <v>8044</v>
       </c>
       <c r="D2" t="n">
-        <v>15881</v>
+        <v>13291</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4976</v>
+        <v>302</v>
       </c>
       <c r="C3" t="n">
-        <v>3355</v>
+        <v>3895</v>
       </c>
       <c r="D3" t="n">
-        <v>16622</v>
+        <v>9721</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3990</v>
+        <v>518</v>
       </c>
       <c r="C4" t="n">
-        <v>5373</v>
+        <v>4708</v>
       </c>
       <c r="D4" t="n">
-        <v>11003</v>
+        <v>8435</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2091</v>
+        <v>610</v>
       </c>
       <c r="C5" t="n">
-        <v>5048</v>
+        <v>6491</v>
       </c>
       <c r="D5" t="n">
-        <v>4280</v>
+        <v>4427</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1226</v>
+        <v>455</v>
       </c>
       <c r="C6" t="n">
-        <v>3444</v>
+        <v>7669</v>
       </c>
       <c r="D6" t="n">
-        <v>1310</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>600</v>
+        <v>195</v>
       </c>
       <c r="C7" t="n">
-        <v>2293</v>
+        <v>5513</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1294</v>
+        <v>2261</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>708</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3342</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>3001</v>
+        <v>4248</v>
       </c>
       <c r="D2" t="n">
-        <v>11005</v>
+        <v>9675</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5020</v>
+        <v>442</v>
       </c>
       <c r="C3" t="n">
-        <v>4391</v>
+        <v>5328</v>
       </c>
       <c r="D3" t="n">
-        <v>16140</v>
+        <v>10693</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4383</v>
+        <v>815</v>
       </c>
       <c r="C4" t="n">
-        <v>5079</v>
+        <v>6862</v>
       </c>
       <c r="D4" t="n">
-        <v>11736</v>
+        <v>8670</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2196</v>
+        <v>459</v>
       </c>
       <c r="C5" t="n">
-        <v>5797</v>
+        <v>10198</v>
       </c>
       <c r="D5" t="n">
-        <v>4659</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1075</v>
+        <v>180</v>
       </c>
       <c r="C6" t="n">
-        <v>4335</v>
+        <v>7206</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
-        <v>2422</v>
+        <v>2215</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>982</v>
+        <v>693</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4410</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
-        <v>7217</v>
+        <v>2761</v>
       </c>
       <c r="D2" t="n">
-        <v>10942</v>
+        <v>7632</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3673</v>
+        <v>291</v>
       </c>
       <c r="C3" t="n">
-        <v>3313</v>
+        <v>4241</v>
       </c>
       <c r="D3" t="n">
-        <v>14445</v>
+        <v>9779</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4068</v>
+        <v>541</v>
       </c>
       <c r="C4" t="n">
-        <v>4636</v>
+        <v>5776</v>
       </c>
       <c r="D4" t="n">
-        <v>12097</v>
+        <v>8394</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2778</v>
+        <v>431</v>
       </c>
       <c r="C5" t="n">
-        <v>5394</v>
+        <v>7603</v>
       </c>
       <c r="D5" t="n">
-        <v>5604</v>
+        <v>4305</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1374</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>4981</v>
+        <v>7020</v>
       </c>
       <c r="D6" t="n">
-        <v>1770</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>49</v>
       </c>
       <c r="C7" t="n">
-        <v>3274</v>
+        <v>3064</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1551</v>
+        <v>814</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3408</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>4652</v>
+        <v>10699</v>
       </c>
       <c r="D2" t="n">
-        <v>8623</v>
+        <v>8071</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3433</v>
+        <v>173</v>
       </c>
       <c r="C3" t="n">
-        <v>4462</v>
+        <v>3031</v>
       </c>
       <c r="D3" t="n">
-        <v>13326</v>
+        <v>8825</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3635</v>
+        <v>370</v>
       </c>
       <c r="C4" t="n">
-        <v>4101</v>
+        <v>4815</v>
       </c>
       <c r="D4" t="n">
-        <v>12160</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3013</v>
+        <v>438</v>
       </c>
       <c r="C5" t="n">
-        <v>5197</v>
+        <v>6480</v>
       </c>
       <c r="D5" t="n">
-        <v>6235</v>
+        <v>4839</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1652</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>5324</v>
+        <v>7308</v>
       </c>
       <c r="D6" t="n">
-        <v>2168</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>3948</v>
+        <v>5031</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>2006</v>
+        <v>1850</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>516</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5572</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>7026</v>
+        <v>13829</v>
       </c>
       <c r="D2" t="n">
-        <v>8868</v>
+        <v>7169</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2876</v>
+        <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>4019</v>
+        <v>5933</v>
       </c>
       <c r="D3" t="n">
-        <v>11849</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3093</v>
+        <v>246</v>
       </c>
       <c r="C4" t="n">
-        <v>4178</v>
+        <v>3778</v>
       </c>
       <c r="D4" t="n">
-        <v>11969</v>
+        <v>8210</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2980</v>
+        <v>375</v>
       </c>
       <c r="C5" t="n">
-        <v>4615</v>
+        <v>5530</v>
       </c>
       <c r="D5" t="n">
-        <v>6898</v>
+        <v>5271</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1987</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>5275</v>
+        <v>6843</v>
       </c>
       <c r="D6" t="n">
-        <v>2686</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>737</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>4485</v>
+        <v>6077</v>
       </c>
       <c r="D7" t="n">
-        <v>922</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2748</v>
+        <v>3252</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1119</v>
+        <v>1077</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8248</v>
+        <v>1733</v>
       </c>
       <c r="C2" t="n">
-        <v>3960</v>
+        <v>8313</v>
       </c>
       <c r="D2" t="n">
-        <v>6139</v>
+        <v>14287</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3901</v>
+        <v>226</v>
       </c>
       <c r="C2" t="n">
-        <v>3879</v>
+        <v>21278</v>
       </c>
       <c r="D2" t="n">
-        <v>6526</v>
+        <v>11490</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3952</v>
+        <v>71</v>
       </c>
       <c r="C3" t="n">
-        <v>5099</v>
+        <v>8218</v>
       </c>
       <c r="D3" t="n">
-        <v>12632</v>
+        <v>7456</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4328</v>
+        <v>160</v>
       </c>
       <c r="C4" t="n">
-        <v>5841</v>
+        <v>4635</v>
       </c>
       <c r="D4" t="n">
-        <v>12390</v>
+        <v>7866</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1973</v>
+        <v>301</v>
       </c>
       <c r="C5" t="n">
-        <v>7133</v>
+        <v>4641</v>
       </c>
       <c r="D5" t="n">
-        <v>6322</v>
+        <v>5562</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>680</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>5532</v>
+        <v>6158</v>
       </c>
       <c r="D6" t="n">
-        <v>2119</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="C7" t="n">
-        <v>2693</v>
+        <v>6397</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1096</v>
+        <v>4385</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>1897</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>601</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7623</v>
+        <v>3026</v>
       </c>
       <c r="C2" t="n">
-        <v>4723</v>
+        <v>7247</v>
       </c>
       <c r="D2" t="n">
-        <v>17503</v>
+        <v>15464</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3502</v>
+        <v>576</v>
       </c>
       <c r="C3" t="n">
-        <v>2027</v>
+        <v>3282</v>
       </c>
       <c r="D3" t="n">
-        <v>1670</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5661</v>
+        <v>2002</v>
       </c>
       <c r="C2" t="n">
-        <v>6407</v>
+        <v>5166</v>
       </c>
       <c r="D2" t="n">
-        <v>14167</v>
+        <v>14614</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4572</v>
+        <v>1532</v>
       </c>
       <c r="C3" t="n">
-        <v>3063</v>
+        <v>4871</v>
       </c>
       <c r="D3" t="n">
-        <v>4207</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1555</v>
+        <v>294</v>
       </c>
       <c r="C4" t="n">
-        <v>1230</v>
+        <v>2095</v>
       </c>
       <c r="D4" t="n">
-        <v>1517</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>190</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5872</v>
+        <v>1521</v>
       </c>
       <c r="C2" t="n">
-        <v>8914</v>
+        <v>10393</v>
       </c>
       <c r="D2" t="n">
-        <v>30063</v>
+        <v>17209</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4205</v>
+        <v>1459</v>
       </c>
       <c r="C3" t="n">
-        <v>4229</v>
+        <v>4333</v>
       </c>
       <c r="D3" t="n">
-        <v>5497</v>
+        <v>5973</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2597</v>
+        <v>801</v>
       </c>
       <c r="C4" t="n">
-        <v>2242</v>
+        <v>3730</v>
       </c>
       <c r="D4" t="n">
-        <v>1987</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>698</v>
+        <v>173</v>
       </c>
       <c r="C5" t="n">
-        <v>765</v>
+        <v>1307</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>218</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5682</v>
+        <v>1243</v>
       </c>
       <c r="C2" t="n">
-        <v>4919</v>
+        <v>8554</v>
       </c>
       <c r="D2" t="n">
-        <v>22150</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4106</v>
+        <v>1229</v>
       </c>
       <c r="C3" t="n">
-        <v>5779</v>
+        <v>6652</v>
       </c>
       <c r="D3" t="n">
-        <v>8844</v>
+        <v>7340</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2900</v>
+        <v>976</v>
       </c>
       <c r="C4" t="n">
-        <v>3242</v>
+        <v>3999</v>
       </c>
       <c r="D4" t="n">
-        <v>2566</v>
+        <v>2817</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>412</v>
       </c>
       <c r="C5" t="n">
-        <v>1528</v>
+        <v>2628</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>362</v>
+        <v>131</v>
       </c>
       <c r="C6" t="n">
-        <v>534</v>
+        <v>819</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>847</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6940</v>
+        <v>1400</v>
       </c>
       <c r="C2" t="n">
-        <v>2949</v>
+        <v>12869</v>
       </c>
       <c r="D2" t="n">
-        <v>24915</v>
+        <v>22289</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3591</v>
+        <v>1021</v>
       </c>
       <c r="C3" t="n">
-        <v>4374</v>
+        <v>6646</v>
       </c>
       <c r="D3" t="n">
-        <v>9637</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2161</v>
+        <v>951</v>
       </c>
       <c r="C4" t="n">
-        <v>3777</v>
+        <v>5367</v>
       </c>
       <c r="D4" t="n">
-        <v>3150</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1112</v>
+        <v>595</v>
       </c>
       <c r="C5" t="n">
-        <v>1781</v>
+        <v>3271</v>
       </c>
       <c r="D5" t="n">
-        <v>1200</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>410</v>
+        <v>236</v>
       </c>
       <c r="C6" t="n">
-        <v>693</v>
+        <v>1747</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7105</v>
+        <v>1015</v>
       </c>
       <c r="C2" t="n">
-        <v>7197</v>
+        <v>11437</v>
       </c>
       <c r="D2" t="n">
-        <v>25806</v>
+        <v>31436</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4380</v>
+        <v>982</v>
       </c>
       <c r="C3" t="n">
-        <v>3021</v>
+        <v>8494</v>
       </c>
       <c r="D3" t="n">
-        <v>11601</v>
+        <v>9926</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2505</v>
+        <v>853</v>
       </c>
       <c r="C4" t="n">
-        <v>4065</v>
+        <v>5918</v>
       </c>
       <c r="D4" t="n">
-        <v>4424</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1471</v>
+        <v>667</v>
       </c>
       <c r="C5" t="n">
-        <v>2931</v>
+        <v>4249</v>
       </c>
       <c r="D5" t="n">
-        <v>1556</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>710</v>
+        <v>361</v>
       </c>
       <c r="C6" t="n">
-        <v>1311</v>
+        <v>2443</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>234</v>
+        <v>149</v>
       </c>
       <c r="C7" t="n">
-        <v>515</v>
+        <v>1129</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>254</v>
+        <v>420</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6251</v>
+        <v>962</v>
       </c>
       <c r="C2" t="n">
-        <v>4863</v>
+        <v>6953</v>
       </c>
       <c r="D2" t="n">
-        <v>32829</v>
+        <v>24584</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4707</v>
+        <v>1412</v>
       </c>
       <c r="C3" t="n">
-        <v>4614</v>
+        <v>12281</v>
       </c>
       <c r="D3" t="n">
-        <v>13038</v>
+        <v>11276</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2975</v>
+        <v>616</v>
       </c>
       <c r="C4" t="n">
-        <v>3379</v>
+        <v>7828</v>
       </c>
       <c r="D4" t="n">
-        <v>5625</v>
+        <v>4110</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1744</v>
+        <v>333</v>
       </c>
       <c r="C5" t="n">
-        <v>3501</v>
+        <v>2394</v>
       </c>
       <c r="D5" t="n">
-        <v>2059</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>999</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>2166</v>
+        <v>1106</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>416</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>930</v>
+        <v>411</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>389</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
